--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="493">
   <si>
     <t>Filename</t>
   </si>
@@ -808,673 +808,691 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9956,0.0006,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.5760,0.0066,0.0003,0.3777</t>
-  </si>
-  <si>
-    <t>0.1023,0.0003,0.0002,0.9647</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9733,0.0045,0.0075,0.0008</t>
+  </si>
+  <si>
+    <t>0.0027,0.0001,0.0003,0.9986</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0053,0.0009,0.0002,0.9976</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
+    <t>0.9999,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.7205,0.0004,0.3605,0.0001</t>
+  </si>
+  <si>
+    <t>0.0654,0.0007,0.9542,0.0001</t>
+  </si>
+  <si>
+    <t>0.1584,0.0020,0.8781,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0012,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.9877,0.0006,0.0114,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0097,0.9933,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9992,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9805,0.0002,0.0107,0.0001</t>
+  </si>
+  <si>
+    <t>0.1600,0.0053,0.7773,0.0024</t>
+  </si>
+  <si>
+    <t>0.0010,0.0001,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0211,0.0008,0.9742,0.0008</t>
+  </si>
+  <si>
+    <t>0.0253,0.0000,0.9874,0.0000</t>
+  </si>
+  <si>
+    <t>0.7165,0.0001,0.3945,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9991,0.0010</t>
+  </si>
+  <si>
+    <t>0.0407,0.9760,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0899,0.3540,0.2547,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.9997,0.0009</t>
+  </si>
+  <si>
+    <t>0.0013,0.9978,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9896,0.0012,0.0065,0.0003</t>
+  </si>
+  <si>
+    <t>0.9975,0.0001,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.5435,0.4803,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9988,0.0025,0.0001</t>
+  </si>
+  <si>
+    <t>0.0163,0.4507,0.4887,0.0013</t>
+  </si>
+  <si>
+    <t>0.0500,0.0000,0.9283,0.0006</t>
+  </si>
+  <si>
+    <t>0.0034,0.0078,0.9875,0.0016</t>
+  </si>
+  <si>
+    <t>0.0041,0.0004,0.9880,0.0080</t>
+  </si>
+  <si>
+    <t>0.0001,0.2537,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0017,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0048,0.5864,0.0006,0.7995</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0033,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0042,0.0032,0.9910,0.0002</t>
+  </si>
+  <si>
+    <t>0.0022,0.0000,0.9977,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0006,0.9988,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0782,0.9978,0.0009</t>
+  </si>
+  <si>
+    <t>0.9981,0.0013,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0019,0.9994,0.0200</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9930,0.9958,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0438,0.9995,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.0012,0.9986,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9975,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.9979,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.3270,0.0001,0.8344,0.0001</t>
+  </si>
+  <si>
+    <t>0.9876,0.0053,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.7637,0.9610,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0584,0.9957,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9967,0.5066,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0008,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0011,0.0002,0.0008,0.9989</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9879,0.5539,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9835,0.9429,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.7612,0.9800,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.9833,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9868,0.6362,0.0001</t>
+  </si>
+  <si>
+    <t>0.9839,0.0312,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9941,0.0046,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9984,0.0012,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0029,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.5834,0.0002,0.5375,0.0000</t>
-  </si>
-  <si>
-    <t>0.0021,0.0014,0.9956,0.0004</t>
-  </si>
-  <si>
-    <t>0.1324,0.0002,0.9284,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0026,0.9987,0.0002</t>
-  </si>
-  <si>
-    <t>0.3315,0.0001,0.7901,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0046,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0626,0.9641,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9505,0.0015,0.0246,0.0007</t>
-  </si>
-  <si>
-    <t>0.2563,0.0037,0.6784,0.0012</t>
-  </si>
-  <si>
-    <t>0.0044,0.0024,0.9939,0.0002</t>
-  </si>
-  <si>
-    <t>0.0583,0.0006,0.9318,0.0008</t>
-  </si>
-  <si>
-    <t>0.6491,0.0000,0.5937,0.0000</t>
-  </si>
-  <si>
-    <t>0.0269,0.0012,0.9771,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.9990,0.0006</t>
-  </si>
-  <si>
-    <t>0.0038,0.9972,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.0143,0.9519,0.0312,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0015,0.9996,0.0022</t>
-  </si>
-  <si>
-    <t>0.0004,0.9992,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9768,0.0019,0.0181,0.0003</t>
-  </si>
-  <si>
-    <t>0.9280,0.0001,0.1080,0.0004</t>
-  </si>
-  <si>
-    <t>0.4069,0.6546,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0073,0.9675,0.0186,0.0012</t>
-  </si>
-  <si>
-    <t>0.0455,0.0004,0.9211,0.0020</t>
-  </si>
-  <si>
-    <t>0.0143,0.0183,0.9703,0.0006</t>
-  </si>
-  <si>
-    <t>0.0317,0.0002,0.9322,0.0051</t>
-  </si>
-  <si>
-    <t>0.0001,0.4196,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9995,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0015,0.9995,0.0007</t>
-  </si>
-  <si>
-    <t>0.0009,0.4911,0.0003,0.9178</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0040,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0009,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0207,0.9961,0.0002</t>
-  </si>
-  <si>
-    <t>0.1197,0.0001,0.9099,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0300,0.9976,0.0008</t>
-  </si>
-  <si>
-    <t>0.9978,0.0015,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0005,0.9995,0.0038</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0012,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9892,0.9957,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0049,0.9996,0.0003</t>
-  </si>
-  <si>
-    <t>0.0016,0.0030,0.9937,0.0018</t>
-  </si>
-  <si>
-    <t>0.0000,0.9991,0.9954,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0054,0.9954,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9927,0.0001,0.0139,0.0000</t>
-  </si>
-  <si>
-    <t>0.9887,0.0034,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.0036,0.0004,0.9969,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9941,0.9326,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.8954,0.9873,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0044,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9969,0.8448,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0001,0.9997</t>
+    <t>0.0000,0.0000,0.9999,0.0041</t>
+  </si>
+  <si>
+    <t>0.1252,0.0070,0.8331,0.0003</t>
+  </si>
+  <si>
+    <t>0.9596,0.0001,0.0106,0.0023</t>
+  </si>
+  <si>
+    <t>0.0085,0.0002,0.9928,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0037,0.9954,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9991,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.8609,0.1934,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.0271,0.0047,0.9429,0.0035</t>
+  </si>
+  <si>
+    <t>0.2269,0.0001,0.8594,0.0000</t>
+  </si>
+  <si>
+    <t>0.6809,0.0202,0.0974,0.0023</t>
+  </si>
+  <si>
+    <t>0.7153,0.0022,0.2144,0.0011</t>
+  </si>
+  <si>
+    <t>0.0002,0.0014,0.0012,0.9992</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9604,0.0252,0.0054,0.0001</t>
+  </si>
+  <si>
+    <t>0.0621,0.9402,0.0035,0.0001</t>
+  </si>
+  <si>
+    <t>0.9946,0.0037,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0007,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.8407,0.9892,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0113,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0128,0.0010,0.9780,0.0002</t>
+  </si>
+  <si>
+    <t>0.0024,0.0005,0.9959,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0000,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.7700,0.0005,0.2562,0.0003</t>
+  </si>
+  <si>
+    <t>0.0265,0.0001,0.9764,0.0005</t>
+  </si>
+  <si>
+    <t>0.1389,0.0004,0.8765,0.0002</t>
+  </si>
+  <si>
+    <t>0.0627,0.0000,0.0001,0.9853</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.9976,0.9770,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0738,0.9431,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.6249,0.0003,0.0197,0.3069</t>
+  </si>
+  <si>
+    <t>0.0004,0.0010,0.9987,0.0037</t>
+  </si>
+  <si>
+    <t>0.9910,0.0000,0.0084,0.0003</t>
+  </si>
+  <si>
+    <t>0.0154,0.9899,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9858,0.0097,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9950,0.0029,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.1701,0.0920,0.4021,0.0002</t>
+  </si>
+  <si>
+    <t>0.9869,0.0037,0.0031,0.0000</t>
+  </si>
+  <si>
+    <t>0.9954,0.0024,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0005,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0009,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.5387,0.4557,0.0049,0.0002</t>
+  </si>
+  <si>
+    <t>0.8705,0.1675,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0143,0.0100,0.9782,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9906,0.0077,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0011,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9940,0.0046,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.0046,0.0007,0.9967,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0484,0.9987,0.0006</t>
+  </si>
+  <si>
+    <t>0.0019,0.0004,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0506,0.9941,0.0017</t>
+  </si>
+  <si>
+    <t>0.0003,0.0006,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9993,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.0006,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0056,0.0013,0.9915,0.0005</t>
+  </si>
+  <si>
+    <t>0.0597,0.0019,0.9266,0.0003</t>
+  </si>
+  <si>
+    <t>0.7800,0.0257,0.0862,0.0004</t>
+  </si>
+  <si>
+    <t>0.0054,0.1652,0.9430,0.0001</t>
+  </si>
+  <si>
+    <t>0.7958,0.0010,0.2446,0.0000</t>
+  </si>
+  <si>
+    <t>0.1268,0.0007,0.8658,0.0004</t>
+  </si>
+  <si>
+    <t>0.0047,0.0037,0.9881,0.0009</t>
+  </si>
+  <si>
+    <t>0.6118,0.6360,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0054,0.9955,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9742,0.0477,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8331,0.2270,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0115,0.9900,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.2250,0.2786,0.0527,0.0030</t>
+  </si>
+  <si>
+    <t>0.9971,0.0001,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.9867,0.0014,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.1836,0.0077,0.7564,0.0016</t>
+  </si>
+  <si>
+    <t>0.1151,0.0041,0.8279,0.0060</t>
+  </si>
+  <si>
+    <t>0.0008,0.0002,0.9981,0.0008</t>
+  </si>
+  <si>
+    <t>0.0058,0.0130,0.9698,0.0041</t>
+  </si>
+  <si>
+    <t>0.0107,0.0808,0.9699,0.0007</t>
+  </si>
+  <si>
+    <t>0.0019,0.0006,0.9966,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0109,0.9921,0.0022</t>
+  </si>
+  <si>
+    <t>0.9983,0.0009,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9987,0.0004,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0016,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9960,0.0039,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9967,0.0019,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0005,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9996,0.0019</t>
+  </si>
+  <si>
+    <t>0.0227,0.3496,0.6479,0.0030</t>
+  </si>
+  <si>
+    <t>0.9921,0.0002,0.0045,0.0006</t>
+  </si>
+  <si>
+    <t>0.0173,0.0000,0.9919,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.0022,0.9958,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0639,0.9977,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0027,0.0022,0.9929,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0048,0.9959,0.0005</t>
+  </si>
+  <si>
+    <t>0.0639,0.0017,0.9106,0.0024</t>
+  </si>
+  <si>
+    <t>0.9887,0.0002,0.0045,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0015,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9969,0.0025,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0018,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0006,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0009,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0016,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0085,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.0154,0.0143,0.9545,0.0003</t>
+  </si>
+  <si>
+    <t>0.0360,0.0000,0.9806,0.0000</t>
+  </si>
+  <si>
+    <t>0.0062,0.0008,0.9710,0.0315</t>
+  </si>
+  <si>
+    <t>0.1557,0.0006,0.8624,0.0001</t>
+  </si>
+  <si>
+    <t>0.0123,0.0011,0.9647,0.0099</t>
+  </si>
+  <si>
+    <t>0.9969,0.0000,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.0008,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0078,0.0000,0.0004,0.9972</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0011,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0003,0.9998</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.0002,0.9998</t>
-  </si>
-  <si>
-    <t>0.0001,0.9955,0.1423,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9973,0.9921,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9924,0.9548,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.8094,0.6524,0.0030</t>
-  </si>
-  <si>
-    <t>0.0000,0.9814,0.9943,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9912,0.7768,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0007,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0025,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9950,0.0080,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0006</t>
-  </si>
-  <si>
-    <t>0.0006,0.0023,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.9848,0.0001,0.0115,0.0002</t>
-  </si>
-  <si>
-    <t>0.0016,0.0004,0.9978,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0042,0.9955,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9986,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.9458,0.0859,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.3458,0.0020,0.5173,0.0109</t>
-  </si>
-  <si>
-    <t>0.4547,0.0019,0.4809,0.0005</t>
-  </si>
-  <si>
-    <t>0.2502,0.3431,0.0156,0.1099</t>
-  </si>
-  <si>
-    <t>0.9794,0.0011,0.0081,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0145,0.0001,0.9992</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0083,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9974,0.9927,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.5091,0.1807,0.0532,0.0000</t>
-  </si>
-  <si>
-    <t>0.8819,0.1248,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0018,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.8805,0.9978,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0869,0.9953,0.0000</t>
-  </si>
-  <si>
-    <t>0.0054,0.0016,0.9883,0.0001</t>
-  </si>
-  <si>
-    <t>0.0095,0.0046,0.9837,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0983,0.0002,0.9223,0.0002</t>
-  </si>
-  <si>
-    <t>0.0442,0.0002,0.9607,0.0009</t>
-  </si>
-  <si>
-    <t>0.9842,0.0006,0.0052,0.0003</t>
-  </si>
-  <si>
-    <t>0.0722,0.0002,0.0002,0.9734</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0000,0.0002,0.9994</t>
-  </si>
-  <si>
-    <t>0.0000,0.9970,0.9169,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9970,0.0020,0.0005</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0269,0.9731,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.6664,0.0000,0.0023,0.4485</t>
-  </si>
-  <si>
-    <t>0.0009,0.0021,0.9971,0.0059</t>
-  </si>
-  <si>
-    <t>0.9920,0.0000,0.0063,0.0004</t>
-  </si>
-  <si>
-    <t>0.3392,0.6752,0.0029,0.0006</t>
-  </si>
-  <si>
-    <t>0.9930,0.0048,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9907,0.0028,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.0804,0.0285,0.7378,0.0001</t>
-  </si>
-  <si>
-    <t>0.9353,0.0016,0.0598,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0011,0.0004,0.0015</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9907,0.0022,0.0000,0.0012</t>
-  </si>
-  <si>
-    <t>0.9808,0.0183,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9905,0.0099,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.0170,0.9974,0.0005</t>
-  </si>
-  <si>
-    <t>0.9996,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0005,0.0010,0.0008</t>
-  </si>
-  <si>
-    <t>0.9769,0.0289,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0017,1.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9723,0.0272,0.0028,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0147,0.9976,0.0006</t>
-  </si>
-  <si>
-    <t>0.0050,0.0006,0.9941,0.0013</t>
-  </si>
-  <si>
-    <t>0.0003,0.0227,0.9983,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9995,0.0013</t>
-  </si>
-  <si>
-    <t>0.0270,0.0037,0.9634,0.0005</t>
-  </si>
-  <si>
-    <t>0.0071,0.0008,0.9898,0.0003</t>
-  </si>
-  <si>
-    <t>0.7938,0.0123,0.1208,0.0002</t>
-  </si>
-  <si>
-    <t>0.0489,0.0053,0.9230,0.0003</t>
-  </si>
-  <si>
-    <t>0.0311,0.5140,0.3920,0.0001</t>
-  </si>
-  <si>
-    <t>0.0417,0.0052,0.9176,0.0004</t>
-  </si>
-  <si>
-    <t>0.1137,0.0019,0.8540,0.0015</t>
-  </si>
-  <si>
-    <t>0.0064,0.0012,0.9900,0.0007</t>
-  </si>
-  <si>
-    <t>0.0106,0.9917,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0718,0.9487,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.9867,0.0217,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0063,0.9948,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0056,0.9947,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9070,0.0269,0.0136,0.0006</t>
-  </si>
-  <si>
-    <t>0.9952,0.0001,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.9550,0.0025,0.0119,0.0023</t>
-  </si>
-  <si>
-    <t>0.1755,0.0087,0.6906,0.0021</t>
-  </si>
-  <si>
-    <t>0.0120,0.0070,0.9712,0.0049</t>
-  </si>
-  <si>
-    <t>0.0011,0.0013,0.9967,0.0012</t>
-  </si>
-  <si>
-    <t>0.0010,0.0061,0.9925,0.0024</t>
-  </si>
-  <si>
-    <t>0.0008,0.0487,0.9963,0.0001</t>
-  </si>
-  <si>
-    <t>0.0042,0.0019,0.9907,0.0002</t>
-  </si>
-  <si>
-    <t>0.0083,0.0074,0.9713,0.0019</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9964,0.0030,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0012,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0009,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,1.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0633,0.0315,0.7817,0.0077</t>
-  </si>
-  <si>
-    <t>0.9878,0.0005,0.0063,0.0011</t>
-  </si>
-  <si>
-    <t>0.0025,0.0001,0.9975,0.0000</t>
-  </si>
-  <si>
-    <t>0.0059,0.0015,0.9901,0.0005</t>
-  </si>
-  <si>
-    <t>0.0015,0.0200,0.9928,0.0010</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0016,0.0012,0.9958,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0011,0.9981,0.0014</t>
-  </si>
-  <si>
-    <t>0.8333,0.0005,0.0984,0.0021</t>
-  </si>
-  <si>
-    <t>0.9692,0.0001,0.0302,0.0001</t>
-  </si>
-  <si>
-    <t>0.9967,0.0000,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0008,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0010,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0014,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0013,0.9987,0.0002</t>
-  </si>
-  <si>
-    <t>0.0013,0.0093,0.9944,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0024,0.9992,0.0003</t>
-  </si>
-  <si>
-    <t>0.0110,0.0494,0.9155,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.0002,0.9983,0.0003</t>
-  </si>
-  <si>
-    <t>0.0011,0.0077,0.9576,0.1463</t>
-  </si>
-  <si>
-    <t>0.0009,0.0023,0.9969,0.0003</t>
-  </si>
-  <si>
-    <t>0.0037,0.0005,0.9923,0.0011</t>
-  </si>
-  <si>
-    <t>0.9784,0.0002,0.0050,0.0052</t>
-  </si>
-  <si>
-    <t>0.0008,0.0028,0.0000,0.9992</t>
-  </si>
-  <si>
-    <t>0.0019,0.0001,0.0017,0.9980</t>
-  </si>
-  <si>
-    <t>0.9933,0.0001,0.0002,0.0018</t>
+    <t>0.0000,0.0000,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.9944,0.0001,0.0000,0.0018</t>
   </si>
 </sst>
 </file>
@@ -1860,7 +1878,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1874,7 +1892,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1888,7 +1906,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1902,7 +1920,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1916,7 +1934,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1930,7 +1948,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1944,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1958,7 +1976,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1972,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1986,7 +2004,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2000,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2014,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2025,10 +2043,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2042,7 +2060,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2056,7 +2074,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2070,7 +2088,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2081,10 +2099,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2098,7 +2116,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2112,7 +2130,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2126,7 +2144,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2140,7 +2158,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2154,7 +2172,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2168,7 +2186,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2182,7 +2200,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2196,7 +2214,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2210,7 +2228,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2224,7 +2242,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2235,10 +2253,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2252,7 +2270,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2266,7 +2284,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2277,10 +2295,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2294,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2308,7 +2326,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2322,7 +2340,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2336,7 +2354,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2347,10 +2365,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2364,7 +2382,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2375,10 +2393,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2392,7 +2410,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2406,7 +2424,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2420,7 +2438,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2434,7 +2452,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2448,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2462,7 +2480,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2473,10 +2491,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2490,7 +2508,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2504,7 +2522,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>283</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2518,7 +2536,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2532,7 +2550,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2546,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2560,7 +2578,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2574,7 +2592,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2588,7 +2606,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2602,7 +2620,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2616,7 +2634,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2630,7 +2648,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2644,7 +2662,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2658,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2672,7 +2690,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2686,7 +2704,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2700,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2714,7 +2732,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2728,7 +2746,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2742,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2756,7 +2774,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2770,7 +2788,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2784,7 +2802,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2798,7 +2816,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>285</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2809,10 +2827,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2826,7 +2844,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2840,7 +2858,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2854,7 +2872,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2865,10 +2883,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2882,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2896,7 +2914,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2910,7 +2928,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2924,7 +2942,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2938,7 +2956,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2952,7 +2970,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2966,7 +2984,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2980,7 +2998,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2991,10 +3009,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3008,7 +3026,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3022,7 +3040,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3036,7 +3054,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3050,7 +3068,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3064,7 +3082,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3078,7 +3096,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3092,7 +3110,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3106,7 +3124,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3120,7 +3138,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3134,7 +3152,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>350</v>
+        <v>275</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3148,7 +3166,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3162,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3176,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3190,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>272</v>
+        <v>354</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3204,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3218,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3232,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3246,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3260,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>272</v>
+        <v>355</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3274,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3288,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3302,7 +3320,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3316,7 +3334,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3330,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3344,7 +3362,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3358,7 +3376,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3372,7 +3390,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>283</v>
+        <v>361</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3386,7 +3404,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3400,7 +3418,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3414,7 +3432,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3428,7 +3446,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>358</v>
+        <v>285</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3442,7 +3460,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3456,7 +3474,7 @@
         <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3467,10 +3485,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3484,7 +3502,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3498,7 +3516,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3512,7 +3530,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3526,7 +3544,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3540,7 +3558,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3554,7 +3572,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3568,7 +3586,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3582,7 +3600,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3596,7 +3614,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3607,10 +3625,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3624,7 +3642,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3638,7 +3656,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3652,7 +3670,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3666,7 +3684,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3680,7 +3698,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3694,7 +3712,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>379</v>
+        <v>355</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3708,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3722,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3736,7 +3754,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3750,7 +3768,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3764,7 +3782,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3778,7 +3796,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3792,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3803,10 +3821,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3820,7 +3838,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3831,10 +3849,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3848,7 +3866,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3862,7 +3880,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>391</v>
+        <v>339</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3876,7 +3894,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>391</v>
+        <v>339</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4002,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4044,7 +4062,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4097,7 +4115,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D162" t="s">
         <v>405</v>
@@ -4156,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4170,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4184,7 +4202,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>272</v>
+        <v>409</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4212,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>273</v>
+        <v>410</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4226,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4240,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4254,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4268,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4282,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4296,7 +4314,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4310,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4324,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4338,7 +4356,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>273</v>
+        <v>419</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4352,7 +4370,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4366,7 +4384,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4380,7 +4398,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4394,7 +4412,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4408,7 +4426,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4422,7 +4440,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4436,7 +4454,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4450,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4464,7 +4482,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4478,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4492,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4506,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4517,10 +4535,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4531,10 +4549,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4545,10 +4563,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4559,10 +4577,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4576,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4590,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4601,10 +4619,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D198" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4618,7 +4636,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4632,7 +4650,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4643,10 +4661,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4660,7 +4678,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4671,10 +4689,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4688,7 +4706,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4702,7 +4720,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4716,7 +4734,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4730,7 +4748,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4744,7 +4762,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4758,7 +4776,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4772,7 +4790,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4786,7 +4804,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4800,7 +4818,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4814,7 +4832,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4828,7 +4846,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4842,7 +4860,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4856,7 +4874,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4870,7 +4888,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4884,7 +4902,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4898,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>272</v>
+        <v>459</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4912,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>272</v>
+        <v>379</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4926,7 +4944,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4940,7 +4958,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4954,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4968,7 +4986,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4982,7 +5000,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4996,7 +5014,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5010,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5024,7 +5042,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5038,7 +5056,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5052,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5066,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5077,10 +5095,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5094,7 +5112,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5108,7 +5126,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5122,7 +5140,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>353</v>
+        <v>473</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5136,7 +5154,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>271</v>
+        <v>474</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5150,7 +5168,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>470</v>
+        <v>355</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5164,7 +5182,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5178,7 +5196,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>472</v>
+        <v>379</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5192,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>415</v>
+        <v>476</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5206,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5220,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5234,7 +5252,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5248,7 +5266,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5262,7 +5280,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5276,7 +5294,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5290,7 +5308,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5304,7 +5322,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5318,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5332,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5346,7 +5364,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5360,7 +5378,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5374,7 +5392,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5388,7 +5406,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>391</v>
+        <v>490</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5402,7 +5420,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>337</v>
+        <v>491</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5416,7 +5434,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
